--- a/public/templates/student-import-sample.xlsx
+++ b/public/templates/student-import-sample.xlsx
@@ -397,38 +397,80 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:X3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>studentCode</v>
       </c>
       <c r="B1" t="str">
+        <v>title</v>
+      </c>
+      <c r="C1" t="str">
         <v>fullname</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
+        <v>nickname</v>
+      </c>
+      <c r="E1" t="str">
+        <v>gender</v>
+      </c>
+      <c r="F1" t="str">
+        <v>birthDate</v>
+      </c>
+      <c r="G1" t="str">
+        <v>age</v>
+      </c>
+      <c r="H1" t="str">
+        <v>citizenId</v>
+      </c>
+      <c r="I1" t="str">
         <v>classLevel</v>
       </c>
-      <c r="D1" t="str">
+      <c r="J1" t="str">
         <v>room</v>
       </c>
-      <c r="E1" t="str">
+      <c r="K1" t="str">
         <v>major</v>
       </c>
-      <c r="F1" t="str">
+      <c r="L1" t="str">
         <v>phone</v>
       </c>
-      <c r="G1" t="str">
-        <v>gender</v>
-      </c>
-      <c r="H1" t="str">
-        <v>birthDate</v>
-      </c>
-      <c r="I1" t="str">
-        <v>citizenId</v>
-      </c>
-      <c r="J1" t="str">
-        <v>nickname</v>
+      <c r="M1" t="str">
+        <v>weight</v>
+      </c>
+      <c r="N1" t="str">
+        <v>height</v>
+      </c>
+      <c r="O1" t="str">
+        <v>bloodType</v>
+      </c>
+      <c r="P1" t="str">
+        <v>nationality</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>religion</v>
+      </c>
+      <c r="R1" t="str">
+        <v>studentType</v>
+      </c>
+      <c r="S1" t="str">
+        <v>disabilityType</v>
+      </c>
+      <c r="T1" t="str">
+        <v>specialAbility</v>
+      </c>
+      <c r="U1" t="str">
+        <v>chronicDisease</v>
+      </c>
+      <c r="V1" t="str">
+        <v>guardianName</v>
+      </c>
+      <c r="W1" t="str">
+        <v>address</v>
+      </c>
+      <c r="X1" t="str">
+        <v>note</v>
       </c>
     </row>
     <row r="2">
@@ -436,31 +478,73 @@
         <v>STD001</v>
       </c>
       <c r="B2" t="str">
-        <v>นายสมชาย ใจดี</v>
+        <v>นาย</v>
       </c>
       <c r="C2" t="str">
+        <v>สมชาย ใจดี</v>
+      </c>
+      <c r="D2" t="str">
+        <v>ชาย</v>
+      </c>
+      <c r="E2" t="str">
+        <v>ชาย</v>
+      </c>
+      <c r="F2" t="str">
+        <v>2008-05-12</v>
+      </c>
+      <c r="G2" t="str">
+        <v>17</v>
+      </c>
+      <c r="H2" t="str">
+        <v>1103700123456</v>
+      </c>
+      <c r="I2" t="str">
         <v>ปวช.1</v>
       </c>
-      <c r="D2" t="str">
+      <c r="J2" t="str">
         <v>1</v>
       </c>
-      <c r="E2" t="str">
+      <c r="K2" t="str">
         <v>คอมพิวเตอร์ธุรกิจ</v>
       </c>
-      <c r="F2" t="str">
+      <c r="L2" t="str">
         <v>0812345678</v>
       </c>
-      <c r="G2" t="str">
-        <v>ชาย</v>
-      </c>
-      <c r="H2" t="str">
-        <v>2008-05-12</v>
-      </c>
-      <c r="I2" t="str">
-        <v>1103700123456</v>
-      </c>
-      <c r="J2" t="str">
-        <v>ชาย</v>
+      <c r="M2" t="str">
+        <v>55</v>
+      </c>
+      <c r="N2" t="str">
+        <v>170</v>
+      </c>
+      <c r="O2" t="str">
+        <v>O</v>
+      </c>
+      <c r="P2" t="str">
+        <v>ไทย</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>พุทธ</v>
+      </c>
+      <c r="R2" t="str">
+        <v>ปกติ</v>
+      </c>
+      <c r="S2" t="str">
+        <v>-</v>
+      </c>
+      <c r="T2" t="str">
+        <v>ดนตรี</v>
+      </c>
+      <c r="U2" t="str">
+        <v>-</v>
+      </c>
+      <c r="V2" t="str">
+        <v>นางสมศรี ใจดี</v>
+      </c>
+      <c r="W2" t="str">
+        <v>123 หมู่ 1 ต.บางรัก อ.เมือง จ.กรุงเทพมหานคร</v>
+      </c>
+      <c r="X2" t="str">
+        <v>-</v>
       </c>
     </row>
     <row r="3">
@@ -468,36 +552,78 @@
         <v>STD002</v>
       </c>
       <c r="B3" t="str">
-        <v>นางสาวสมหญิง รักเรียน</v>
+        <v>นางสาว</v>
       </c>
       <c r="C3" t="str">
+        <v>สมหญิง รักเรียน</v>
+      </c>
+      <c r="D3" t="str">
+        <v>หญิง</v>
+      </c>
+      <c r="E3" t="str">
+        <v>หญิง</v>
+      </c>
+      <c r="F3" t="str">
+        <v>2008-09-20</v>
+      </c>
+      <c r="G3" t="str">
+        <v>17</v>
+      </c>
+      <c r="H3" t="str">
+        <v>1103700654321</v>
+      </c>
+      <c r="I3" t="str">
         <v>ปวช.1</v>
       </c>
-      <c r="D3" t="str">
+      <c r="J3" t="str">
         <v>1</v>
       </c>
-      <c r="E3" t="str">
+      <c r="K3" t="str">
         <v>การบัญชี</v>
       </c>
-      <c r="F3" t="str">
+      <c r="L3" t="str">
         <v>0898765432</v>
       </c>
-      <c r="G3" t="str">
-        <v>หญิง</v>
-      </c>
-      <c r="H3" t="str">
-        <v>2008-09-20</v>
-      </c>
-      <c r="I3" t="str">
-        <v>1103700654321</v>
-      </c>
-      <c r="J3" t="str">
-        <v>หญิง</v>
+      <c r="M3" t="str">
+        <v>48</v>
+      </c>
+      <c r="N3" t="str">
+        <v>160</v>
+      </c>
+      <c r="O3" t="str">
+        <v>A</v>
+      </c>
+      <c r="P3" t="str">
+        <v>ไทย</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>พุทธ</v>
+      </c>
+      <c r="R3" t="str">
+        <v>ปกติ</v>
+      </c>
+      <c r="S3" t="str">
+        <v>-</v>
+      </c>
+      <c r="T3" t="str">
+        <v>กีฬา</v>
+      </c>
+      <c r="U3" t="str">
+        <v>-</v>
+      </c>
+      <c r="V3" t="str">
+        <v>นายสมหมาย รักเรียน</v>
+      </c>
+      <c r="W3" t="str">
+        <v>456 หมู่ 2 ต.บางรัก อ.เมือง จ.กรุงเทพมหานคร</v>
+      </c>
+      <c r="X3" t="str">
+        <v>-</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:X3"/>
   </ignoredErrors>
 </worksheet>
 </file>